--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9ebcfe40dd314e2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rf455392e18524865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R7dd818cccf4942ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re63913fc780a48ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rb18677b69a7d4027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rc55eebe7bccc4ccf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R341f26a482484d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R3eae46634f9a46b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rff0560248fa542d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcce85be60a3742ec"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rc55eebe7bccc4ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R341f26a482484d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R3eae46634f9a46b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rff0560248fa542d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcce85be60a3742ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rdb35c83f7f134362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R357c87fa9d394e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R6664b2fb6c784ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R26d32078c65a483b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra67c81f963dd4252"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rdb35c83f7f134362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R357c87fa9d394e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R6664b2fb6c784ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R26d32078c65a483b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Ra67c81f963dd4252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R3af7631b117a41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R904605622aa24f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R171548ca2162430b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re35cc4ddcfa048cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re87aa8720d014ff8"/>
   </x:sheets>
 </x:workbook>
 </file>
